--- a/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T17:25:50+00:00</t>
+    <t>2024-04-22T17:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T17:40:56+00:00</t>
+    <t>2024-04-23T07:57:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T07:57:57+00:00</t>
+    <t>2024-04-23T09:09:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T09:09:38+00:00</t>
+    <t>2024-04-23T11:50:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T11:50:53+00:00</t>
+    <t>2024-04-23T12:02:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T12:02:00+00:00</t>
+    <t>2024-04-23T12:54:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T12:54:40+00:00</t>
+    <t>2024-04-23T13:53:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-23T13:53:01+00:00</t>
+    <t>2024-04-24T07:17:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T07:17:51+00:00</t>
+    <t>2024-04-24T07:20:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T07:20:21+00:00</t>
+    <t>2024-04-24T07:47:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T07:47:38+00:00</t>
+    <t>2024-04-25T08:18:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:18:53+00:00</t>
+    <t>2024-04-25T11:48:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T11:48:40+00:00</t>
+    <t>2024-04-25T14:16:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T14:16:56+00:00</t>
+    <t>2024-05-02T08:42:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-02T08:42:54+00:00</t>
+    <t>2024-05-02T08:55:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-02T08:55:07+00:00</t>
+    <t>2024-05-03T14:18:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-03T14:18:47+00:00</t>
+    <t>2024-05-03T14:27:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-03T14:27:04+00:00</t>
+    <t>2024-05-03T14:31:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-03T14:31:09+00:00</t>
+    <t>2024-05-03T15:46:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-03T15:46:37+00:00</t>
+    <t>2024-05-04T12:21:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T12:21:39+00:00</t>
+    <t>2024-05-04T13:53:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
+++ b/ig/DM-37/ValueSet-JDV-bdpm-all.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T13:53:38+00:00</t>
+    <t>2024-05-04T15:01:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
